--- a/Data/EC/NIT-8904052551.xlsx
+++ b/Data/EC/NIT-8904052551.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AFDE7D6-1150-444B-86B6-E195A97A5573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03E974EE-F087-4E0F-BB56-E6A27F9755D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{798D58BB-15BC-473A-AE19-FCC6FC994ABD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E7DEC7DC-5912-4F8B-8D00-9301C7F27BBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -71,94 +71,94 @@
     <t>BERONICA VEGA GALVIS</t>
   </si>
   <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>1912</t>
+  </si>
+  <si>
+    <t>1911</t>
+  </si>
+  <si>
+    <t>1910</t>
+  </si>
+  <si>
+    <t>1909</t>
+  </si>
+  <si>
+    <t>1908</t>
+  </si>
+  <si>
+    <t>1907</t>
+  </si>
+  <si>
+    <t>1906</t>
+  </si>
+  <si>
+    <t>1905</t>
+  </si>
+  <si>
+    <t>1904</t>
+  </si>
+  <si>
+    <t>1903</t>
+  </si>
+  <si>
+    <t>1902</t>
+  </si>
+  <si>
+    <t>1901</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>1712</t>
+  </si>
+  <si>
+    <t>1711</t>
+  </si>
+  <si>
     <t>1710</t>
-  </si>
-  <si>
-    <t>1711</t>
-  </si>
-  <si>
-    <t>1712</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>1901</t>
-  </si>
-  <si>
-    <t>1902</t>
-  </si>
-  <si>
-    <t>1903</t>
-  </si>
-  <si>
-    <t>1904</t>
-  </si>
-  <si>
-    <t>1905</t>
-  </si>
-  <si>
-    <t>1906</t>
-  </si>
-  <si>
-    <t>1907</t>
-  </si>
-  <si>
-    <t>1908</t>
-  </si>
-  <si>
-    <t>1909</t>
-  </si>
-  <si>
-    <t>1910</t>
-  </si>
-  <si>
-    <t>1911</t>
-  </si>
-  <si>
-    <t>1912</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2003</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -257,9 +257,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -272,7 +270,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -472,23 +472,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -516,10 +516,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -557,22 +557,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>667900</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>430650</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C6FB06A-CC17-9AA6-B026-1ADBF9BC3A90}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B051451-7663-16F3-73D5-C1559F9F5864}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -594,7 +594,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="921900" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -923,23 +923,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9827F82A-5D34-4627-AA98-0FE399C8C61C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9DC3A15-DC79-486A-AB74-B4825C1F00CC}">
   <dimension ref="B2:J51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -952,7 +952,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -963,7 +963,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -974,7 +974,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -985,8 +985,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>42</v>
       </c>
@@ -1001,8 +1001,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1017,8 +1017,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>43</v>
       </c>
@@ -1033,8 +1033,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>44</v>
       </c>
@@ -1053,7 +1053,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1082,7 +1082,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="18">
-        <v>29509</v>
+        <v>30208</v>
       </c>
       <c r="G16" s="18">
         <v>781242</v>
@@ -1105,7 +1105,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>12</v>
       </c>
       <c r="F17" s="18">
-        <v>29509</v>
+        <v>31249</v>
       </c>
       <c r="G17" s="18">
         <v>781242</v>
@@ -1128,7 +1128,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>13</v>
       </c>
       <c r="F18" s="18">
-        <v>29509</v>
+        <v>31249</v>
       </c>
       <c r="G18" s="18">
         <v>781242</v>
@@ -1151,7 +1151,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="18">
-        <v>29509</v>
+        <v>31249</v>
       </c>
       <c r="G19" s="18">
         <v>781242</v>
@@ -1174,7 +1174,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>15</v>
       </c>
       <c r="F20" s="18">
-        <v>29509</v>
+        <v>31249</v>
       </c>
       <c r="G20" s="18">
         <v>781242</v>
@@ -1197,7 +1197,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>16</v>
       </c>
       <c r="F21" s="18">
-        <v>29509</v>
+        <v>31249</v>
       </c>
       <c r="G21" s="18">
         <v>781242</v>
@@ -1220,7 +1220,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>17</v>
       </c>
       <c r="F22" s="18">
-        <v>29509</v>
+        <v>31249</v>
       </c>
       <c r="G22" s="18">
         <v>781242</v>
@@ -1243,7 +1243,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>18</v>
       </c>
       <c r="F23" s="18">
-        <v>29509</v>
+        <v>31249</v>
       </c>
       <c r="G23" s="18">
         <v>781242</v>
@@ -1266,7 +1266,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>19</v>
       </c>
       <c r="F24" s="18">
-        <v>29509</v>
+        <v>31249</v>
       </c>
       <c r="G24" s="18">
         <v>781242</v>
@@ -1289,7 +1289,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>20</v>
       </c>
       <c r="F25" s="18">
-        <v>29509</v>
+        <v>31249</v>
       </c>
       <c r="G25" s="18">
         <v>781242</v>
@@ -1312,7 +1312,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>21</v>
       </c>
       <c r="F26" s="18">
-        <v>29509</v>
+        <v>31249</v>
       </c>
       <c r="G26" s="18">
         <v>781242</v>
@@ -1335,7 +1335,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1358,7 +1358,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1381,7 +1381,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1404,7 +1404,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1427,7 +1427,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1450,7 +1450,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1473,7 +1473,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1496,7 +1496,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1519,7 +1519,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>30</v>
       </c>
       <c r="F35" s="18">
-        <v>31249</v>
+        <v>29509</v>
       </c>
       <c r="G35" s="18">
         <v>781242</v>
@@ -1542,7 +1542,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>31</v>
       </c>
       <c r="F36" s="18">
-        <v>31249</v>
+        <v>29509</v>
       </c>
       <c r="G36" s="18">
         <v>781242</v>
@@ -1565,7 +1565,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1579,7 +1579,7 @@
         <v>32</v>
       </c>
       <c r="F37" s="18">
-        <v>31249</v>
+        <v>29509</v>
       </c>
       <c r="G37" s="18">
         <v>781242</v>
@@ -1588,7 +1588,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1602,7 +1602,7 @@
         <v>33</v>
       </c>
       <c r="F38" s="18">
-        <v>31249</v>
+        <v>29509</v>
       </c>
       <c r="G38" s="18">
         <v>781242</v>
@@ -1611,7 +1611,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>34</v>
       </c>
       <c r="F39" s="18">
-        <v>31249</v>
+        <v>29509</v>
       </c>
       <c r="G39" s="18">
         <v>781242</v>
@@ -1634,7 +1634,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>35</v>
       </c>
       <c r="F40" s="18">
-        <v>31249</v>
+        <v>29509</v>
       </c>
       <c r="G40" s="18">
         <v>781242</v>
@@ -1657,7 +1657,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>36</v>
       </c>
       <c r="F41" s="18">
-        <v>31249</v>
+        <v>29509</v>
       </c>
       <c r="G41" s="18">
         <v>781242</v>
@@ -1680,7 +1680,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>37</v>
       </c>
       <c r="F42" s="18">
-        <v>31249</v>
+        <v>29509</v>
       </c>
       <c r="G42" s="18">
         <v>781242</v>
@@ -1703,7 +1703,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1717,7 +1717,7 @@
         <v>38</v>
       </c>
       <c r="F43" s="18">
-        <v>31249</v>
+        <v>29509</v>
       </c>
       <c r="G43" s="18">
         <v>781242</v>
@@ -1726,7 +1726,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>39</v>
       </c>
       <c r="F44" s="18">
-        <v>31249</v>
+        <v>29509</v>
       </c>
       <c r="G44" s="18">
         <v>781242</v>
@@ -1749,7 +1749,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="21" t="s">
         <v>8</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>40</v>
       </c>
       <c r="F45" s="24">
-        <v>30208</v>
+        <v>29509</v>
       </c>
       <c r="G45" s="24">
         <v>781242</v>
@@ -1772,7 +1772,7 @@
       <c r="I45" s="25"/>
       <c r="J45" s="26"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="32" t="s">
         <v>50</v>
       </c>
@@ -1783,7 +1783,7 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="32" t="s">
         <v>49</v>
       </c>
